--- a/output/pdf_financials_xlsx/DATT.xlsx
+++ b/output/pdf_financials_xlsx/DATT.xlsx
@@ -2191,16 +2191,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.432824</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.060261</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.347191</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.990542</v>
       </c>
     </row>
     <row r="93">
@@ -3494,7 +3494,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3676,7 +3680,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3968,7 +3976,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>2.432824</v>
       </c>

--- a/output/pdf_financials_xlsx/DATT.xlsx
+++ b/output/pdf_financials_xlsx/DATT.xlsx
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">

--- a/output/pdf_financials_xlsx/DATT.xlsx
+++ b/output/pdf_financials_xlsx/DATT.xlsx
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.514038</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.782036</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.835937</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.703651</v>
       </c>
     </row>
     <row r="65">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.09879499999999999</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.107339</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.093307</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.059058</v>
       </c>
     </row>
     <row r="68">
@@ -2618,16 +2618,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.227887</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.032734</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.002253</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.021434</v>
       </c>
     </row>
     <row r="116">
@@ -4534,7 +4534,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.227887</v>
       </c>
@@ -4666,7 +4670,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
